--- a/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_NV.xlsx
+++ b/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_NV.xlsx
@@ -2,27 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="Re24b870ec7a94cac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="R1b1f9402bceb48b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R5ea2220b4eb9489d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R4c7d48db0e7e4313"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="Rf4c836de573b4fc3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R4d59b71b621a412e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="R52f5020e656745c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="Rdfa01bd736944700"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R15b46f9e35db42d8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="R8d8785fe37ff436a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="Reef3806f9857469c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="Rd96c688aed60452a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R0097bc5cdd4543bb"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="Rb1a1fb76930f45c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R2db5bfe0ef95408e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="Re2a1edb021ed4eac"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="Rba4c2ee532dc4544"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R082634235d2d48c2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="R3567ec0ddef34612"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="Rbb5ebee231ee42d6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="Ra31bbbfcb9004b4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R851e682686ea4ce2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="R0e4f6bf543a24839"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R9405e43353bb476d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R42c5606f73264f98"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="Rf9ba4f199ae04e25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="Rc15f48e492bc44e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="Rfc8c142ae87b48dd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R8649e511f37c410e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="Rff509d90881d4b77"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="R1489f9c599e448b0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="Rb26c59a488164f0c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="Ra5e84d31d48c4228"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R6e4c7fb9801242ae"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="R94a467c00b244321"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R08d173689c5a4705"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R6bfd7d4091964520"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="Re445f3a2888d4856"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="Rb1a54e3a5b71436f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="R412b26b128d44a1e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="Rc65645c1d2814abc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="Rb6d47607327f46d1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="R571eca7a9b604a6a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -3288,6 +3289,41 @@
 </x:worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="13.75" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="51.25" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="19.5" customHeight="1">
+      <x:c r="A1" t="str">
+        <x:v>名前</x:v>
+      </x:c>
+      <x:c r="B1" t="str">
+        <x:v>フランチェスカ・ユリア・エロルディ・セリック</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="19.5" customHeight="1">
+      <x:c r="A2" t="str">
+        <x:v>出身地</x:v>
+      </x:c>
+      <x:c r="B2" t="str">
+        <x:v>カルフェオン</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="19.5" customHeight="1">
+      <x:c r="A3" t="str">
+        <x:v>Other</x:v>
+      </x:c>
+      <x:c r="B3"/>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</x:worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>

--- a/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_NV.xlsx
+++ b/資料/説明(パッシブ・スキル)/黒い砂漠M_説明_NV.xlsx
@@ -2,28 +2,28 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R851e682686ea4ce2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="R0e4f6bf543a24839"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R9405e43353bb476d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="R42c5606f73264f98"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="Rf9ba4f199ae04e25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="Rc15f48e492bc44e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="Rfc8c142ae87b48dd"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R8649e511f37c410e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="Rff509d90881d4b77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="R1489f9c599e448b0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="Rb26c59a488164f0c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="Ra5e84d31d48c4228"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R6e4c7fb9801242ae"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="R94a467c00b244321"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R08d173689c5a4705"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R6bfd7d4091964520"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="Re445f3a2888d4856"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="Rb1a54e3a5b71436f"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="R412b26b128d44a1e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="Rc65645c1d2814abc"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="Rb6d47607327f46d1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="R571eca7a9b604a6a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(①)" sheetId="1" r:id="R53762f89c7e9478a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="パッシブ(②)" sheetId="2" r:id="R79d0192b926b4d63"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(０)" sheetId="3" r:id="R8ff4552177ed4f0f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(1)" sheetId="4" r:id="Rbd8fe328e5c54a75"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(2)" sheetId="5" r:id="R47b4e0c8ddd2454e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(3)" sheetId="6" r:id="R659dd5f6fe294c12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(4)" sheetId="7" r:id="Rca64b6e8c6f746b1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(5)" sheetId="8" r:id="R3d4b44e30d7c4b6e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(6)" sheetId="9" r:id="R09ebca9c2d574f8d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(7)" sheetId="10" r:id="R719cc43e2eda4957"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(8)" sheetId="11" r:id="Rfadcc41c0aac460d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(9)" sheetId="12" r:id="Re4c44b2add094c5d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(10)" sheetId="13" r:id="R4d2558e5f4784284"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(11)" sheetId="14" r:id="R29c263666f294c8f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(12)" sheetId="15" r:id="R3101f577b8cf4a49"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(13)" sheetId="16" r:id="R547a21ee4cb04d36"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(1)" sheetId="17" r:id="Rde60508086d743e5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(2)" sheetId="18" r:id="R84ce9b5fa2514802"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(3)" sheetId="19" r:id="Ra1e8bb16dd864039"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ラバムスキル(4)" sheetId="20" r:id="R3875d13094944d54"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="スキル(黒精霊の怒り)" sheetId="21" r:id="Rb5cc06b4182f4cac"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="プロフィール" sheetId="22" r:id="R0a8bebfa74a24a77"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2041,7 +2041,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -2069,7 +2069,7 @@
         <x:v>襲いかかる輪</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>襲いかかる輪</x:v>
+        <x:v>襲い掛かる環</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -2086,11 +2086,11 @@
         <x:v>PvE PvP ｜系列 無欠 鮮明 洗練された</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 無欠 鮮明 洗練された</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"전방으로 돌진하여 크라툼으로 올려 친다."</x:v>
       </x:c>
@@ -2101,11 +2101,11 @@
         <x:v>「前方に突進し、クラトゥムで上に突き上げる。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「前方に突進し、クラトゥムで上に突き上げる。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>前方に突進し、クラトゥムで突き上げる。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -2116,11 +2116,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 15초</x:v>
       </x:c>
@@ -2131,37 +2131,55 @@
         <x:v>・再使用待機時間: 15秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 15秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：15秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ1824%x5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ912%x5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9"/>
+      <x:c r="B9" t="str">
         <x:v>・기술 사용 중 슈퍼 아머 , 잡기 불가</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" t="str">
         <x:v>・Super Armor , Grab Immunity while using skill</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" t="str">
         <x:v>・スーパーアーマー、技術使用中に免疫を獲得</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・スーパーアーマー、技術使用中に免疫を獲得</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" t="str">
+        <x:v>・スキル使用中、スーパーアーマー、キャッチ不可</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10"/>
+      <x:c r="B10" t="str">
         <x:v>・타격 성공 시 경직</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" t="str">
         <x:v>・Stiffness on hit</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" t="str">
         <x:v>・打球時の剛性</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・打球時の剛性</x:v>
+      <x:c r="E10" t="str">
+        <x:v>・打撃成功時、硬直</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2181,7 +2199,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -2226,11 +2244,11 @@
         <x:v>PvE PvP ｜系列 守護 無欠 鮮明</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 守護 無欠 鮮明</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"스팅을 휘둘러 적을 견제하며 순간적으로 빠르게 근접하여 적을 올려 친다."</x:v>
       </x:c>
@@ -2241,11 +2259,11 @@
         <x:v>「スティングで敵を牽制しつつ、素早く接近して上方へ攻撃する。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「スティングで敵を牽制しつつ、素早く接近して上方へ攻撃する。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>スティングを振り回して敵を牽制し、瞬時に接近して敵を突き上げる。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -2256,11 +2274,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 15초</x:v>
       </x:c>
@@ -2271,52 +2289,70 @@
         <x:v>・再使用待機時間: 15秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 15秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：15秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ2124%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ1062%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・최대 4 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 4 hits</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・最大4ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・最大4ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・最大4打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10"/>
+      <x:c r="B10" t="str">
         <x:v>・기술 사용 중 슈퍼 아머 , 잡기 불가</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" t="str">
         <x:v>・Super Armor , Grab Immunity while using skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" t="str">
         <x:v>・スーパーアーマー、技術使用中に免疫を獲得</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・スーパーアーマー、技術使用中に免疫を獲得</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" t="str">
+        <x:v>・スキル使用中、スーパーアーマー、キャッチ不可</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
         <x:v>・타격 성공 시 경직</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" t="str">
         <x:v>・Stiffness on hit</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" t="str">
         <x:v>・打球時の剛性</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・打球時の剛性</x:v>
+      <x:c r="E11" t="str">
+        <x:v>・打撃成功時、硬直</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2336,7 +2372,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -2364,7 +2400,7 @@
         <x:v>死者の王</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>死者の王</x:v>
+        <x:v>死者たちの王</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -2381,11 +2417,11 @@
         <x:v>PvE PvP ｜系列 守護 無欠 鮮明</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 守護 無欠 鮮明</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"죽은자들의 왕을 불러낸다. 강력한 힘을 가진 왕은 노바의 신성력을 대가로 죽음의 냉기를 흩뿌린다."</x:v>
       </x:c>
@@ -2396,11 +2432,11 @@
         <x:v>「死者の王を召喚する。強力な王はノヴァの神聖な力と引き換えに死の冷気を撒き散らす。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「死者の王を召喚する。強力な王はノヴァの神聖な力と引き換えに死の冷気を撒き散らす。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>死者たちの王を召喚する。強力な力を持つ王は、ノヴァの神聖力を代償に死の冷気を撒き散らす。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -2411,11 +2447,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 16초</x:v>
       </x:c>
@@ -2426,67 +2462,85 @@
         <x:v>・再使用待機時間: 16秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 16秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：16秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ2872%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ1436%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・최대 5 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 5 hits</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・最大5ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・最大5ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・最大5打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Super Armor while using skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
         <x:v>・타격 성공 시 기절</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" t="str">
         <x:v>・Stun on hit</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" t="str">
         <x:v>・ヒット時に気絶させる</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ヒット時に気絶させる</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" t="str">
+        <x:v>・打撃成功時、気絶</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12"/>
+      <x:c r="B12" t="str">
         <x:v>・기술 사용 시 1.5초 간 전방 가드 부여</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" t="str">
         <x:v>・Forward Guard for 1.5 seconds when using skill</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" t="str">
         <x:v>・技術使用時1.5秒前方ガード</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>・技術使用時1.5秒前方ガード</x:v>
+      <x:c r="E12" t="str">
+        <x:v>・スキル使用時、1.5秒間前方ガード適用</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -2946,7 +3000,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -2974,7 +3028,7 @@
         <x:v>星の輪</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>星の輪</x:v>
+        <x:v>星の環</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -2991,11 +3045,11 @@
         <x:v>PvE PvP ｜系列 無欠 鮮明 洗練された</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 無欠 鮮明 洗練された</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"전방으로 낫을 던지며 항성을 소환한다."</x:v>
       </x:c>
@@ -3006,11 +3060,11 @@
         <x:v>「大鎌を前方に投げ、固定星を召喚する。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「大鎌を前方に投げ、固定星を召喚する。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>前方に鎌を投げながら恒星を召喚する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -3021,11 +3075,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 16초</x:v>
       </x:c>
@@ -3036,67 +3090,112 @@
         <x:v>・再使用待機時間: 16秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 16秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：16秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ2151%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ1075.5%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・최대 2 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 2 hits</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・最大2ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・最大2ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・最大2打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・기술 사용 중 전방 가드</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Forward Guard while using skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・技術使用中の前衛ガード</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術使用中の前衛ガード</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・スキル使用中、前方ガード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
         <x:v>・타격 성공 시 기절</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" t="str">
         <x:v>・Stun on hit</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" t="str">
         <x:v>・ヒット時に気絶させる</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ヒット時に気絶させる</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" t="str">
+        <x:v>・打撃成功時、気絶</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12"/>
+      <x:c r="B12" t="str">
         <x:v>・첫 번째 공격 시 항성 생성</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" t="str">
         <x:v>・Creates a Fixed Star on the first attack</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" t="str">
         <x:v>・最初の攻撃で固定星を作成します</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>・最初の攻撃で固定星を作成します</x:v>
+      <x:c r="E12" t="str">
+        <x:v>・最初の打撃時、恒星生成</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13"/>
+      <x:c r="B13"/>
+      <x:c r="C13"/>
+      <x:c r="D13"/>
+      <x:c r="E13" t="str">
+        <x:v>・恒星</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14" t="str">
+        <x:v>　打撃ダメージ1505.7%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15" t="str">
+        <x:v>　PVP打撃ダメージ752.85%</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3431,7 +3530,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -3459,7 +3558,7 @@
         <x:v>命令：湧き上がる氷の棘</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>命令：湧き上がる氷の棘</x:v>
+        <x:v>命令：湧き起こる氷の棘</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -3476,11 +3575,11 @@
         <x:v>PvE ｜系列 無欠 鮮明 かすかな</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE ｜系列 無欠 鮮明 かすかな</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"적에게 얼음의 기운을 담은 샛별을 휘둘러 피해를 입힌 후 폰에게 명령해 적을 공격한다."</x:v>
       </x:c>
@@ -3491,11 +3590,11 @@
         <x:v>「氷のエネルギーを宿したモーニングスターを振り回してダメージを与え、ポーンに敵を攻撃するように命令します。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「氷のエネルギーを宿したモーニングスターを振り回してダメージを与え、ポーンに敵を攻撃するように命令します。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>氷のオーラを込めたモーニングスターを振り回して敵に冷気を与えた後、ポーンに命令し攻撃する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -3506,11 +3605,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 6초</x:v>
       </x:c>
@@ -3521,97 +3620,133 @@
         <x:v>・再使用待機時間: 6秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 6秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：6秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ1841.56%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ920.78%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・기술 버튼 유지 시 최대 4 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 4 hits when holding the skill button</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・技術ボタン長押しで最大4ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・技術ボタン長押しで最大4ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・スキルボタン長押しで最大4打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Super Armor while using skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="8"/>
+      <x:c r="B11" s="6" t="str">
         <x:v>・타격 성공 시 빙결</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" s="6" t="str">
         <x:v>・Freeze on hit</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" s="6" t="str">
         <x:v>・ヒット時にフリーズ</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ヒット時にフリーズ</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" s="6" t="str">
+        <x:v>・打撃成功時、氷結</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="8"/>
+      <x:c r="B12" s="6" t="str">
+        <x:v>・무기 선택 : 샛별 적용 시</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="str">
+        <x:v>・When Weapon Selection: Morning Star is applied</x:v>
+      </x:c>
+      <x:c r="D12" s="6" t="str">
+        <x:v>・武器選択：モーニングスター適用時</x:v>
+      </x:c>
+      <x:c r="E12" s="6" t="str">
+        <x:v>・武器選択：モーニングスター適用時</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13"/>
+      <x:c r="B13" t="str">
         <x:v>・폰 소환</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C13" t="str">
         <x:v>・Summon Pawn</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D13" t="str">
         <x:v>・サモン・ポーン</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>・サモン・ポーン</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="8" t="str"/>
-      <x:c r="B11" s="6" t="str">
-        <x:v>・무기 선택 : 샛별 적용 시</x:v>
-      </x:c>
-      <x:c r="C11" s="6" t="str">
-        <x:v>・When Weapon Selection: Morning Star is applied</x:v>
-      </x:c>
-      <x:c r="D11" s="6" t="str">
-        <x:v>・武器選択：モーニングスター適用時</x:v>
-      </x:c>
-      <x:c r="E11" s="6" t="str">
-        <x:v>・武器選択：モーニングスター適用時</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="8" t="str"/>
-      <x:c r="B12" s="6" t="str">
+      <x:c r="E13" t="str">
+        <x:v>・ポーン召喚</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14" t="str">
+        <x:v>　打撃ダメージ1315.03%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15" t="str">
+        <x:v>　PVP打撃ダメージ657.52%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16"/>
+      <x:c r="B16" t="str">
         <x:v>・소환 시 10초 간 몬스터 추가 공격력 100 증가</x:v>
       </x:c>
-      <x:c r="C12" s="6" t="str">
+      <x:c r="C16" t="str">
         <x:v>・Extra Damage to Monsters +100 for 10 seconds upon summoning</x:v>
       </x:c>
-      <x:c r="D12" s="6" t="str">
+      <x:c r="D16" t="str">
         <x:v>・召喚時10秒間、モンスターへの追加ダメージ+100</x:v>
       </x:c>
-      <x:c r="E12" s="6" t="str">
-        <x:v>・召喚時10秒間、モンスターへの追加ダメージ+100</x:v>
+      <x:c r="E16" t="str">
+        <x:v>　召喚時に10秒間、モンスター追加攻撃力+100増加</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3631,7 +3766,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -3676,11 +3811,11 @@
         <x:v>PvE ｜系列 無欠 鮮明 かすかな</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE ｜系列 無欠 鮮明 かすかな</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="15" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"적을 연속으로 찌르며 공격한다."</x:v>
       </x:c>
@@ -3691,11 +3826,11 @@
         <x:v>敵を連続貫通して攻撃します。</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>敵を連続貫通して攻撃します。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>敵を連続で刺す攻撃を行う。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 2</x:v>
       </x:c>
@@ -3706,11 +3841,11 @@
         <x:v>・最大使用回数: 2</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 6초</x:v>
       </x:c>
@@ -3721,67 +3856,85 @@
         <x:v>・再使用待機時間: 6秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 6秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：6秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ1122.4%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ561.2%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・최대 6 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 6 hits</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・最大6ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・最大6ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・最大6打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Super Armor while using skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
         <x:v>・타격 성공 시 기절</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" t="str">
         <x:v>・Stun on hit</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" t="str">
         <x:v>・ヒット時に気絶させる</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ヒット時に気絶させる</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" t="str">
+        <x:v>・打撃成功時、気絶</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12"/>
+      <x:c r="B12" t="str">
         <x:v>・마지막 타격 성공 시 넉백</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" t="str">
         <x:v>・Knockback on last hit</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" t="str">
         <x:v>・最後のヒットでノックバック</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>・最後のヒットでノックバック</x:v>
+      <x:c r="E12" t="str">
+        <x:v>・最後の打撃成功時、ノックバック</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3801,7 +3954,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -3829,7 +3982,7 @@
         <x:v>酷寒の懲罰</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>酷寒の懲罰</x:v>
+        <x:v>酷寒の戒め</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -3846,11 +3999,11 @@
         <x:v>PvE PvP ｜系列 守護 無欠 鮮明</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 守護 無欠 鮮明</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"크라툼을 내려찍어 얼음의 기운을 모은 후 적에게 모은 기운을 발사한다."</x:v>
       </x:c>
@@ -3861,11 +4014,11 @@
         <x:v>「クラトゥムを叩きつけて氷のエネルギーを集め、集めたエネルギーを敵に発射する。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「クラトゥムを叩きつけて氷のエネルギーを集め、集めたエネルギーを敵に発射する。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>クラトゥムを振り下ろして氷のオーラを集め、集めた力を放射する。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 2</x:v>
       </x:c>
@@ -3876,11 +4029,11 @@
         <x:v>・最大使用回数: 2</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 6초</x:v>
       </x:c>
@@ -3891,67 +4044,85 @@
         <x:v>・再使用待機時間: 6秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 6秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：6秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ1193.03%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ596.52%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・기술 버튼 유지 시 최대 5 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 5 hits when holding the skill button</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・技術ボタン長押しで最大5ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・技術ボタン長押しで最大5ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・スキルボタン長押しで最大5打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・기술 사용 중 전방 가드</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Forward Guard while using skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・技術使用中の前衛ガード</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術使用中の前衛ガード</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・スキル使用中、前方ガード</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
         <x:v>・타격 성공 시 넉백</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" t="str">
         <x:v>・Knockback on hit</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" t="str">
         <x:v>・ヒット時ノックバック</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ヒット時ノックバック</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" t="str">
+        <x:v>・打撃成功時、ノックバック</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12"/>
+      <x:c r="B12" t="str">
         <x:v>・마지막 타격 성공 시 넉다운</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C12" t="str">
         <x:v>・Knockdown on last hit</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D12" t="str">
         <x:v>・最後のヒットでノックダウン</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>・最後のヒットでノックダウン</x:v>
+      <x:c r="E12" t="str">
+        <x:v>・最後の打撃成功時、ノックダウン</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -3971,7 +4142,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -4016,11 +4187,11 @@
         <x:v>PvE PvP ｜系列 無欠 鮮明 洗練された</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 無欠 鮮明 洗練された</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"스팅의 날카로움을 이용해 적을 연속으로 베어 피해를 입힌다."</x:v>
       </x:c>
@@ -4031,11 +4202,11 @@
         <x:v>スティングの鋭さを利用して敵を連続斬り、ダメージを与えます。</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>スティングの鋭さを利用して敵を連続斬り、ダメージを与えます。</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>スティングの鋭さを利用して敵を連続で斬りつけダメージを与える。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -4046,11 +4217,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 5초</x:v>
       </x:c>
@@ -4061,52 +4232,70 @@
         <x:v>・再使用待機時間: 5秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 5秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：5秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ1479.41%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ739.71%x2</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・기술 버튼 유지 시 최대 2 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 2 hits when holding the skill button</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・技術ボタン長押しで最大2ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・技術ボタン長押しで最大2ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・スキルボタン長押しで最大2打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10"/>
+      <x:c r="B10" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" t="str">
         <x:v>・Super Armor while using skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
         <x:v>・타격 성공 시 넉다운</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" t="str">
         <x:v>・Knockdown on hit</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" t="str">
         <x:v>・ヒット時ノックダウン</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ヒット時ノックダウン</x:v>
+      <x:c r="E11" t="str">
+        <x:v>・打撃成功時、ノックダウン</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4126,7 +4315,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -4171,11 +4360,11 @@
         <x:v>PvE PvP ｜系列 無欠 洗練された かすかな</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 無欠 洗練された かすかな</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvE</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"크라툼을 휘둘러 빙판을 생성한 뒤 나이트를 소환해 공격 명령을 내린다."</x:v>
       </x:c>
@@ -4186,11 +4375,11 @@
         <x:v>「クラトゥムを振り回して氷の板を作り、ナイトを召喚して攻撃命令を下す。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「クラトゥムを振り回して氷の板を作り、ナイトを召喚して攻撃命令を下す。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>クラトゥムを振り回して氷盤を生成した後、ナイトを召喚し攻撃命令を下す。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -4201,11 +4390,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 6초</x:v>
       </x:c>
@@ -4216,112 +4405,148 @@
         <x:v>・再使用待機時間: 6秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 6秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：6秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ909.22%x3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ454.61%x3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・기술 버튼 유지 시 최대 2 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 2 hits when holding the skill button</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・技術ボタン長押しで最大2ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・技術ボタン長押しで最大2ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・スキルボタン長押しで最大2打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10" s="8"/>
+      <x:c r="B10" s="6" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" s="6" t="str">
         <x:v>・Super Armor while using skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" s="6" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" s="6" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11" s="8"/>
+      <x:c r="B11" s="6" t="str">
         <x:v>・타격 성공 시 넉다운</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" s="6" t="str">
         <x:v>・Knockdown on hit</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" s="6" t="str">
         <x:v>・ヒット時ノックダウン</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・ヒット時ノックダウン</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="30" customHeight="1">
-      <x:c r="A10" s="8" t="str"/>
-      <x:c r="B10" s="6" t="str">
+      <x:c r="E11" s="6" t="str">
+        <x:v>・打撃成功時、ノックダウン</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="15" hidden="0" customHeight="1">
+      <x:c r="A12" s="8"/>
+      <x:c r="B12" s="6" t="str">
+        <x:v>・무기 선택 : 샛별 적용 시</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="str">
+        <x:v>・When Weapon Selection: Morning Star is applied</x:v>
+      </x:c>
+      <x:c r="D12" s="6" t="str">
+        <x:v>・武器選択：モーニングスター適用時</x:v>
+      </x:c>
+      <x:c r="E12" s="6" t="str">
+        <x:v>・武器選択：モーニングスター適用時</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="15" hidden="0" customHeight="1">
+      <x:c r="A13" s="8"/>
+      <x:c r="B13" s="6" t="str">
         <x:v>・나이트 소환</x:v>
       </x:c>
-      <x:c r="C10" s="6" t="str">
+      <x:c r="C13" s="6" t="str">
         <x:v>・Summon Knight</x:v>
       </x:c>
-      <x:c r="D10" s="6" t="str">
+      <x:c r="D13" s="6" t="str">
         <x:v>・サモンナイト</x:v>
       </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>・サモンナイト</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="30" customHeight="1">
-      <x:c r="A11" s="8" t="str"/>
-      <x:c r="B11" s="6" t="str">
-        <x:v>・무기 선택 : 샛별 적용 시</x:v>
-      </x:c>
-      <x:c r="C11" s="6" t="str">
-        <x:v>・When Weapon Selection: Morning Star is applied</x:v>
-      </x:c>
-      <x:c r="D11" s="6" t="str">
-        <x:v>・武器選択：モーニングスター適用時</x:v>
-      </x:c>
-      <x:c r="E11" s="6" t="str">
-        <x:v>・武器選択：モーニングスター適用時</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="30" customHeight="1">
-      <x:c r="A12" s="8" t="str"/>
-      <x:c r="B12" s="6" t="str">
+      <x:c r="E13" s="6" t="str">
+        <x:v>・ナイト召喚</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="15" hidden="0" customHeight="1">
+      <x:c r="A14"/>
+      <x:c r="B14"/>
+      <x:c r="C14"/>
+      <x:c r="D14"/>
+      <x:c r="E14" t="str">
+        <x:v>　打撃ダメージ1551.33%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="15" hidden="0" customHeight="1">
+      <x:c r="A15"/>
+      <x:c r="B15"/>
+      <x:c r="C15"/>
+      <x:c r="D15"/>
+      <x:c r="E15" t="str">
+        <x:v>　PVP打撃ダメージ454.61%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="15" hidden="0" customHeight="1">
+      <x:c r="A16"/>
+      <x:c r="B16" t="str">
         <x:v>・소환 시 10초 간 공격 속도 +10%</x:v>
       </x:c>
-      <x:c r="C12" s="6" t="str">
+      <x:c r="C16" t="str">
         <x:v>・Attack Speed +10% for 10 seconds upon summoning</x:v>
       </x:c>
-      <x:c r="D12" s="6" t="str">
+      <x:c r="D16" t="str">
         <x:v>・召喚時10秒間攻撃速度+10%</x:v>
       </x:c>
-      <x:c r="E12" s="6" t="str">
-        <x:v>・召喚時10秒間攻撃速度+10%</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="30" customHeight="1">
-      <x:c r="A13" s="8" t="str"/>
-      <x:c r="B13" s="6" t="str">
+      <x:c r="E16" t="str">
+        <x:v>　召喚時、10秒間、攻撃速度+10%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="15" hidden="0" customHeight="1">
+      <x:c r="A17"/>
+      <x:c r="B17" t="str">
         <x:v>・이동 속도 +10%</x:v>
       </x:c>
-      <x:c r="C13" s="6" t="str">
+      <x:c r="C17" t="str">
         <x:v>・Move Speed +10%</x:v>
       </x:c>
-      <x:c r="D13" s="6" t="str">
+      <x:c r="D17" t="str">
         <x:v>・移動速度 +10%</x:v>
       </x:c>
-      <x:c r="E13" s="6" t="str">
-        <x:v>・移動速度 +10%</x:v>
+      <x:c r="E17" t="str">
+        <x:v>　移動速度+10%</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -4341,7 +4566,7 @@
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
-      <x:c r="A1" s="4" t="str"/>
+      <x:c r="A1" s="4"/>
       <x:c r="B1" s="4" t="str">
         <x:v>韓国語</x:v>
       </x:c>
@@ -4369,7 +4594,7 @@
         <x:v>交差する軌道</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>交差する軌道</x:v>
+        <x:v>すれ違う軌道</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -4386,11 +4611,11 @@
         <x:v>PvE PvP ｜系列 燦爛 洗練された かすかな</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>PvE PvP ｜系列 燦爛 洗練された かすかな</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
-      <x:c r="A4" s="8" t="str"/>
+        <x:v>PvP</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="26.399999618530273" hidden="0" customHeight="1">
+      <x:c r="A4" s="8"/>
       <x:c r="B4" s="6" t="str">
         <x:v>"현란하게 이동하여 적의 빈틈을 찾아 찌르기 공격을 한다."</x:v>
       </x:c>
@@ -4401,11 +4626,11 @@
         <x:v>「目まぐるしく動き、敵の防御の隙を突いて突撃する。」</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>「目まぐるしく動き、敵の防御の隙を突いて突撃する。」</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="30" customHeight="1">
-      <x:c r="A5" s="8" t="str"/>
+        <x:v>華麗に移動し、敵の隙を見つけて突きを放つ。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="15" hidden="0" customHeight="1">
+      <x:c r="A5" s="8"/>
       <x:c r="B5" s="6" t="str">
         <x:v>・최대 사용 횟수 : 1</x:v>
       </x:c>
@@ -4416,11 +4641,11 @@
         <x:v>・最大使用回数: 1</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>・最大使用回数: 1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="30" customHeight="1">
-      <x:c r="A6" s="8" t="str"/>
+        <x:v>最大使用回数：1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="15" hidden="0" customHeight="1">
+      <x:c r="A6" s="8"/>
       <x:c r="B6" s="6" t="str">
         <x:v>・재사용 대기시간 : 5초</x:v>
       </x:c>
@@ -4431,52 +4656,70 @@
         <x:v>・再使用待機時間: 5秒</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>・再使用待機時間: 5秒</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="30" customHeight="1">
-      <x:c r="A7" s="8" t="str"/>
-      <x:c r="B7" s="6" t="str">
+        <x:v>再使用待機時間：5秒</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="15" hidden="0" customHeight="1">
+      <x:c r="A7" s="8"/>
+      <x:c r="B7" s="6"/>
+      <x:c r="C7" s="6"/>
+      <x:c r="D7" s="6"/>
+      <x:c r="E7" s="6" t="str">
+        <x:v>・打撃ダメージ1904.48%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="15" hidden="0" customHeight="1">
+      <x:c r="A8" s="8"/>
+      <x:c r="B8" s="6"/>
+      <x:c r="C8" s="6"/>
+      <x:c r="D8" s="6"/>
+      <x:c r="E8" s="6" t="str">
+        <x:v>・PVP打撃ダメージ952.24%</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="15" hidden="0" customHeight="1">
+      <x:c r="A9" s="8"/>
+      <x:c r="B9" s="6" t="str">
         <x:v>・기술 버튼 유지 시 최대 2 타격</x:v>
       </x:c>
-      <x:c r="C7" s="6" t="str">
+      <x:c r="C9" s="6" t="str">
         <x:v>・Max 2 hits when holding the skill button</x:v>
       </x:c>
-      <x:c r="D7" s="6" t="str">
+      <x:c r="D9" s="6" t="str">
         <x:v>・技術ボタン長押しで最大2ヒット</x:v>
       </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>・技術ボタン長押しで最大2ヒット</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="30" customHeight="1">
-      <x:c r="A8" s="8" t="str"/>
-      <x:c r="B8" s="6" t="str">
+      <x:c r="E9" s="6" t="str">
+        <x:v>・スキルボタン長押しで最大2打撃</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="15" hidden="0" customHeight="1">
+      <x:c r="A10"/>
+      <x:c r="B10" t="str">
         <x:v>・기술 사용 중 슈퍼 아머</x:v>
       </x:c>
-      <x:c r="C8" s="6" t="str">
+      <x:c r="C10" t="str">
         <x:v>・Super Armor while using skill</x:v>
       </x:c>
-      <x:c r="D8" s="6" t="str">
+      <x:c r="D10" t="str">
         <x:v>・技術使用時のスーパーアーマー</x:v>
       </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>・技術使用時のスーパーアーマー</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="30" customHeight="1">
-      <x:c r="A9" s="8" t="str"/>
-      <x:c r="B9" s="6" t="str">
+      <x:c r="E10" t="str">
+        <x:v>・スキル使用中、スーパーアーマー</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="15" hidden="0" customHeight="1">
+      <x:c r="A11"/>
+      <x:c r="B11" t="str">
         <x:v>・타격 성공 시 경직</x:v>
       </x:c>
-      <x:c r="C9" s="6" t="str">
+      <x:c r="C11" t="str">
         <x:v>・Stiffness on hit</x:v>
       </x:c>
-      <x:c r="D9" s="6" t="str">
+      <x:c r="D11" t="str">
         <x:v>・打球時の剛性</x:v>
       </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>・打球時の剛性</x:v>
+      <x:c r="E11" t="str">
+        <x:v>・打撃成功時、硬直</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
